--- a/backend/signal_logs/signals_2026-08-06.xlsx
+++ b/backend/signal_logs/signals_2026-08-06.xlsx
@@ -761,6 +761,11 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Closed down ~19.65 (-11.7% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -850,6 +855,11 @@
           <t>NSE:PNBHOUSING26AUG1160CE</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Closed down ~29.9 (-6.7% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -939,6 +949,11 @@
           <t>NSE:BANDHANBNK26AUG175PE</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Closed up ~5.29 (+1.7% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1028,6 +1043,11 @@
           <t>NSE:CHOLAFIN26AUG1940CE</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Closed down ~53.55 (-4.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1117,6 +1137,11 @@
           <t>NSE:JUBLFOOD26AUG475CE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Closed down ~15.55 (-1.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1204,6 +1229,11 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:BIOCON26AUG435CE</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Closed up ~14.35 (+15.3% from entry, EOD estimate)</t>
         </is>
       </c>
     </row>
